--- a/assets/constructions/examples/ctd_tko_chamfer_preparting.xlsx
+++ b/assets/constructions/examples/ctd_tko_chamfer_preparting.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF6"/>
+  <dimension ref="A1:AK6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,56 +589,71 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MB-07T045-02-10R    1025</t>
+          <t>VE08020CH45 RVTX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CoroCut-MB</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>CoroCut MB -size 07</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>SANDVIK</t>
-        </is>
-      </c>
+          <t>Mini-V</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PMNSO</t>
+          <t>PMKNSH</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
-        <v>5.8</v>
+        <v>4.65</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N2" t="n">
-        <v>4</v>
-      </c>
+        <v>4.6</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
         <v>0.2</v>
       </c>
@@ -654,11 +669,11 @@
         <v>45</v>
       </c>
       <c r="S2" t="n">
-        <v>42</v>
+        <v>1.3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>COR_MB:07</t>
+          <t>VARGUS_V08</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,22 +683,18 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>VTX</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>PVD TIALN+TIN</t>
+          <t>TiAlN</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>HC</t>
-        </is>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr">
         <is>
           <t>VHM</t>
@@ -691,22 +702,39 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>ZXA</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
-      <c r="AD2" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
         <v>0</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2020 / Sandvik Web-site</t>
+          <t>2021/Groovex Vargus</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>25.48</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
+        <v>2342.47</v>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
@@ -819,6 +847,25 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AG3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>3064.15</v>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -929,6 +976,25 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AG4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>3064.15</v>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1039,46 +1105,67 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AG5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VE08020CH45 RVTX</t>
+          <t>MB-07T045-02-10R    1025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mini-V</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+          <t>CoroCut-MB</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CoroCut MB -size 07</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SANDVIK</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PMKNSH</t>
+          <t>PMNSO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J6" t="n">
-        <v>4.65</v>
+        <v>5.8</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N6" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4</v>
+      </c>
       <c r="O6" t="n">
         <v>0.2</v>
       </c>
@@ -1094,11 +1181,11 @@
         <v>45</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3</v>
+        <v>42</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>VARGUS_V08</t>
+          <t>COR_MB:07</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1108,18 +1195,22 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>VTX</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>TiAlN</t>
+          <t>PVD TIALN+TIN</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Y6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
       <c r="Z6" t="inlineStr">
         <is>
           <t>VHM</t>
@@ -1127,20 +1218,33 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>ZXA</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
         <v>0</v>
       </c>
-      <c r="AD6" t="inlineStr"/>
+      <c r="AD6" t="n">
+        <v>0.002</v>
+      </c>
       <c r="AE6" t="n">
         <v>0</v>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2021/Groovex Vargus</t>
+          <t>2020 / Sandvik Web-site</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>PMNSO</t>
         </is>
       </c>
     </row>
